--- a/ab_meter_output/xlsx/ABMeter_10_16_130_50.xlsx
+++ b/ab_meter_output/xlsx/ABMeter_10_16_130_50.xlsx
@@ -208,12 +208,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$B$2:$B$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -240,12 +240,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$C$2:$C$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -272,12 +272,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$D$2:$D$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -304,12 +304,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$E$2:$E$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -336,12 +336,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$F$2:$F$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -368,12 +368,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$G$2:$G$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -400,12 +400,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$H$2:$H$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -432,12 +432,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$I$2:$I$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -464,12 +464,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$J$2:$J$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -496,12 +496,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$K$2:$K$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +528,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$L$2:$L$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +560,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$M$2:$M$7</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -679,12 +679,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$B$2:$B$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -711,12 +711,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$C$2:$C$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -743,12 +743,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$D$2:$D$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -775,12 +775,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$E$2:$E$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -807,12 +807,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$F$2:$F$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -839,12 +839,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$G$2:$G$7</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -958,12 +958,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$B$2:$B$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -990,12 +990,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$C$2:$C$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1022,12 +1022,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$D$2:$D$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1054,12 +1054,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$E$2:$E$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -1086,12 +1086,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$F$2:$F$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -1118,12 +1118,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$G$2:$G$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -1150,12 +1150,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$H$2:$H$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -1182,12 +1182,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$I$2:$I$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -1214,12 +1214,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$J$2:$J$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -1246,12 +1246,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$K$2:$K$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -1278,12 +1278,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$L$2:$L$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -1310,12 +1310,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$M$2:$M$7</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -1429,12 +1429,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$B$2:$B$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -1461,12 +1461,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$C$2:$C$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1493,12 +1493,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$D$2:$D$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1525,12 +1525,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$E$2:$E$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -1557,12 +1557,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$F$2:$F$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -1589,12 +1589,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$G$2:$G$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -1621,12 +1621,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$H$2:$H$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -1653,12 +1653,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$I$2:$I$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -1685,12 +1685,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$J$2:$J$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -1717,12 +1717,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$K$2:$K$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -1749,12 +1749,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$L$2:$L$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -1781,12 +1781,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$M$2:$M$7</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -1900,12 +1900,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$B$2:$B$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -1932,12 +1932,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$C$2:$C$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1964,12 +1964,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$D$2:$D$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1996,12 +1996,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$E$2:$E$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -2028,12 +2028,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$F$2:$F$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -2060,12 +2060,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$G$2:$G$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -2092,12 +2092,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$H$2:$H$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -2124,12 +2124,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$I$2:$I$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -2156,12 +2156,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$J$2:$J$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -2188,12 +2188,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$K$2:$K$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -2220,12 +2220,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$L$2:$L$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -2252,12 +2252,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$M$2:$M$7</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -2371,12 +2371,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$B$2:$B$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -2403,12 +2403,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$C$2:$C$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -2435,12 +2435,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$D$2:$D$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -2467,12 +2467,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$E$2:$E$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -2499,12 +2499,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$F$2:$F$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -2531,12 +2531,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$G$2:$G$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -2563,12 +2563,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$H$2:$H$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -2595,12 +2595,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$I$2:$I$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -2627,12 +2627,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$J$2:$J$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -2659,12 +2659,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$K$2:$K$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -2691,12 +2691,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$L$2:$L$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -2723,12 +2723,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$M$2:$M$7</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -2842,12 +2842,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$B$2:$B$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -2874,12 +2874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$C$2:$C$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -2906,12 +2906,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$D$2:$D$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -2938,12 +2938,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$E$2:$E$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -2970,12 +2970,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$F$2:$F$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -3002,12 +3002,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$G$2:$G$7</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -3121,12 +3121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$B$2:$B$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -3153,12 +3153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$C$2:$C$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -3185,12 +3185,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$D$2:$D$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -3217,12 +3217,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$E$2:$E$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -3249,12 +3249,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$F$2:$F$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -3281,12 +3281,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$G$2:$G$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -3313,12 +3313,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$H$2:$H$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -3345,12 +3345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$I$2:$I$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -3377,12 +3377,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$J$2:$J$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -3409,12 +3409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$K$2:$K$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -3441,12 +3441,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$L$2:$L$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -3473,12 +3473,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$M$2:$M$7</f>
+              <f>'Demand_Data_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -3592,12 +3592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$B$2:$B$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -3624,12 +3624,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$C$2:$C$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -3656,12 +3656,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$D$2:$D$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -3688,12 +3688,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$E$2:$E$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -3720,12 +3720,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$F$2:$F$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -3752,12 +3752,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$G$2:$G$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -3784,12 +3784,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$H$2:$H$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -3816,12 +3816,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$I$2:$I$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -3848,12 +3848,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$J$2:$J$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -3880,12 +3880,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$K$2:$K$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -3912,12 +3912,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$L$2:$L$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -3944,12 +3944,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$M$2:$M$7</f>
+              <f>'Diagnostic_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -4063,12 +4063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$B$2:$B$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -4095,12 +4095,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$C$2:$C$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -4127,12 +4127,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$D$2:$D$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -4159,12 +4159,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$E$2:$E$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -4191,12 +4191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$F$2:$F$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -4223,12 +4223,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$G$2:$G$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -4255,12 +4255,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$H$2:$H$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -4287,12 +4287,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$I$2:$I$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -4319,12 +4319,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$J$2:$J$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -4351,12 +4351,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$K$2:$K$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -4383,12 +4383,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$L$2:$L$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -4415,12 +4415,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$M$2:$M$7</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -4534,12 +4534,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$B$2:$B$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -4566,12 +4566,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$C$2:$C$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -4598,12 +4598,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$D$2:$D$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -4630,12 +4630,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$E$2:$E$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -4662,12 +4662,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$F$2:$F$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -4694,12 +4694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$G$2:$G$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -4726,12 +4726,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$H$2:$H$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -4758,12 +4758,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$I$2:$I$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -4790,12 +4790,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$J$2:$J$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -4822,12 +4822,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$K$2:$K$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -4854,12 +4854,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$L$2:$L$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -4886,12 +4886,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$M$2:$M$7</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$M$2:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -4966,7 +4966,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -4993,7 +4993,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5020,7 +5020,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5047,7 +5047,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5074,7 +5074,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5101,7 +5101,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5128,7 +5128,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5155,7 +5155,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5182,7 +5182,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5209,7 +5209,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5236,7 +5236,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5546,7 +5546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5836,7 +5836,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -5930,7 +5930,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6024,7 +6024,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6112,194 +6112,6 @@
         <v>2</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>2399.999756</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>2399.999756</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6315,7 +6127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6380,7 +6192,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6405,7 +6217,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6430,7 +6242,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6449,56 +6261,6 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6514,7 +6276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6740,7 +6502,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6834,7 +6596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6928,7 +6690,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -7016,194 +6778,6 @@
         <v>0</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>1403</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>304</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1403</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>304</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7219,7 +6793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7344,7 +6918,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -7393,7 +6967,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -7442,7 +7016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -7485,104 +7059,6 @@
         <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -7598,7 +7074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7859,71 +7335,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>53.257355</v>
+        <v>48.402405</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>57.92841</v>
+        <v>52.484978</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>51.001518</v>
+        <v>46.820866</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0.004291</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>54.062428</v>
+        <v>49.236084</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>53.956177</v>
+        <v>49.138004</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4.107093</v>
+        <v>3.420535</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>7.611907</v>
+        <v>6.961078</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4337.584473</v>
+        <v>4313.118164</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>4302.146973</v>
+        <v>4283.645508</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>4317.899902</v>
+        <v>4302.740723</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>4319.210449</v>
+        <v>4299.834473</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>4318.337402</v>
+        <v>4298.916504</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>34.314125</v>
+        <v>29.667421</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.794614</v>
+        <v>0.690114</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>2503.382324</v>
+        <v>2491.706055</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2493.612305</v>
+        <v>2479.79126</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>2483.365723</v>
+        <v>2475.144775</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>2493.453369</v>
+        <v>2482.213867</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>59.995113</v>
+        <v>59.974606</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>2</v>
@@ -7932,71 +7408,71 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>53.208317</v>
+        <v>48.843761</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>57.376709</v>
+        <v>53.527077</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>50.82988</v>
+        <v>48.390144</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.004291</v>
+        <v>0.003984</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>53.804966</v>
+        <v>50.253662</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>53.710976</v>
+        <v>50.167839</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3.837374</v>
+        <v>3.297935</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>7.144487</v>
+        <v>6.573802</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4340.078125</v>
+        <v>4311.813477</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>4303.580078</v>
+        <v>4282.809082</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>4317.662598</v>
+        <v>4299.278809</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>4320.439941</v>
+        <v>4297.967285</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>4319.647949</v>
+        <v>4297.129395</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>35.148151</v>
+        <v>29.905714</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.813681</v>
+        <v>0.695946</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>2503.978027</v>
+        <v>2490.037842</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2495.161133</v>
+        <v>2479.672119</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2483.246582</v>
+        <v>2473.714844</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>2494.128662</v>
+        <v>2481.141602</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>60.000973</v>
+        <v>59.962887</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>2</v>
@@ -8005,219 +7481,73 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>47.286747</v>
+        <v>52.00684</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>50.327221</v>
+        <v>56.371391</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>45.32515</v>
+        <v>49.98394</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0.003984</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>47.646374</v>
+        <v>52.787395</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>47.568726</v>
+        <v>52.681137</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.917875</v>
+        <v>3.788334</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>6.134021</v>
+        <v>7.191063</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4341.974121</v>
+        <v>4311.807617</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>4307.878418</v>
+        <v>4281.977539</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>4320.171387</v>
+        <v>4296.656738</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>4323.341309</v>
+        <v>4296.813965</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>4322.507812</v>
+        <v>4295.937988</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>33.83754</v>
+        <v>30.501446</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.782822</v>
+        <v>0.7100070000000001</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>2504.931152</v>
+        <v>2489.203857</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>2496.829346</v>
+        <v>2479.79126</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>2485.629639</v>
+        <v>2472.404297</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2495.796875</v>
+        <v>2480.466553</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>60.023434</v>
+        <v>59.992184</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>49.530323</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>53.735497</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>48.794724</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.003984</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>50.686848</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>50.6092</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>3.089515</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>6.104651</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4337.222168</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4302.38916</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>4316.11377</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>4318.574707</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>4317.741699</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>34.075832</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.789205</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>2502.54834</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>2493.731445</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>2482.88916</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>2493.056396</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>60.023434</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>52.558537</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>55.782913</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>50.118801</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.003984</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>52.820084</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>52.742435</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>3.261155</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>6.183171</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>4337.105469</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>4300.956055</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>4312.890137</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0.008219000000000001</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>4316.983887</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>4316.192871</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>35.624737</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.8253740000000001</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>2501.476074</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>2493.850586</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>2481.102051</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>2492.142822</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>60.015621</v>
-      </c>
-      <c r="W7" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8233,7 +7563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8520,396 +7850,238 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>117571.507812</v>
+        <v>104529.257812</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>132772.640625</v>
+        <v>117357.421875</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>118216.5625</v>
+        <v>106315.414062</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>368560.71875</v>
+        <v>328202.09375</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>62840.132812</v>
+        <v>60094.707031</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>57205.40625</v>
+        <v>56197.335938</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>45564.710938</v>
+        <v>45899.300781</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>165610.25</v>
+        <v>162191.34375</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>133316.078125</v>
+        <v>120562.429688</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>144576.1875</v>
+        <v>130109.671875</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>126704.132812</v>
+        <v>115827.695312</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>404596.375</v>
+        <v>366499.78125</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-88.19004099999999</v>
+        <v>-86.70135500000001</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-91.83575399999999</v>
+        <v>-90.19884500000001</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-93.30127</v>
+        <v>-91.78756</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-91.083916</v>
+        <v>-89.557129</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>-88.64511899999999</v>
+        <v>-86.36116</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-92.149292</v>
+        <v>-90.385689</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-93.211868</v>
+        <v>-91.902817</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>-91.435654</v>
+        <v>-89.66894499999999</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>99.98284099999999</v>
+        <v>99.989403</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>99.980232</v>
+        <v>99.987785</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>99.96421100000001</v>
+        <v>99.97803500000001</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>99.97576100000001</v>
+        <v>99.985077</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>118086.804688</v>
+        <v>105864.4375</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>131703.8125</v>
+        <v>118820.492188</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>117579.359375</v>
+        <v>110023.851562</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>367370</v>
+        <v>334708.78125</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>61638.640625</v>
+        <v>59793.960938</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>55838.253906</v>
+        <v>58868.816406</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>45722.890625</v>
+        <v>46910.921875</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>163199.78125</v>
+        <v>165573.703125</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>133202.6875</v>
+        <v>121598.078125</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>143069.09375</v>
+        <v>132595.203125</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>126162.007812</v>
+        <v>119606.617188</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>402433.78125</v>
+        <v>373799.90625</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-88.651978</v>
+        <v>-87.06094400000001</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-92.056091</v>
+        <v>-89.611458</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-93.19712800000001</v>
+        <v>-91.98809799999999</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-91.29528000000001</v>
+        <v>-89.54257200000001</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-87.669579</v>
+        <v>-86.36116</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-91.33607499999999</v>
+        <v>-90.385689</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-92.14662199999999</v>
+        <v>-91.902817</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>8.34557</v>
+        <v>-89.66894499999999</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>99.98775500000001</v>
+        <v>99.989403</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>99.982208</v>
+        <v>99.987785</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>99.971046</v>
+        <v>99.97803500000001</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>99.980339</v>
+        <v>99.985077</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>106856.984375</v>
+        <v>112917.921875</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>117331.054688</v>
+        <v>126870.546875</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>106446.953125</v>
+        <v>113982.828125</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>330635</v>
+        <v>353771.3125</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>57017.683594</v>
+        <v>62870.144531</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>52811.902344</v>
+        <v>58188.886719</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>44623.394531</v>
+        <v>47224.851562</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>154452.984375</v>
+        <v>168283.875</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>121135.21875</v>
+        <v>129241.929688</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>128713.257812</v>
+        <v>139552.78125</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>115467.867188</v>
+        <v>123380.210938</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>365316.34375</v>
+        <v>392174.9375</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-88.212975</v>
+        <v>-87.369415</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-91.156937</v>
+        <v>-90.91223100000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-92.187515</v>
+        <v>-92.383392</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-90.622536</v>
+        <v>-90.20291899999999</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-87.669579</v>
+        <v>-86.977852</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-91.33607499999999</v>
+        <v>-90.564804</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-92.14662199999999</v>
+        <v>-92.00505800000001</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>8.34557</v>
+        <v>-89.949951</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>99.98775500000001</v>
+        <v>99.98922</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>99.982208</v>
+        <v>99.98777800000001</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>99.971046</v>
+        <v>99.977936</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>99.980339</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>110106.492188</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>122028.585938</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>112619.507812</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>344754.59375</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>56767.699219</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>55162.160156</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>44390.144531</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>156320</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>123871.765625</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>133910.09375</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>121077.914062</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>378859.78125</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-88.88748200000001</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-91.127251</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>-93.014076</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>-90.996971</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>-88.397797</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>-92.16548899999999</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>-93.489075</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>10.745414</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>99.99065400000001</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>99.98782300000001</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>99.979767</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>99.98608400000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>113811.09375</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>124911.0625</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>112712.71875</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>351434.875</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>65321.085938</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>60463.605469</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>51806.167969</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>177590.859375</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>131228.515625</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>138771.21875</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>124051.539062</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>394051.28125</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-86.72740899999999</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-90.01222199999999</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>-90.859589</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>-89.219398</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>-88.122742</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>-91.330566</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>-92.871758</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>-90.87336000000001</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>99.98891399999999</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>99.98505400000001</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>99.976944</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>99.983643</v>
+        <v>99.984978</v>
       </c>
     </row>
   </sheetData>
@@ -8924,7 +8096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9013,126 +8185,76 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>44847880.796948</v>
+        <v>44848020.555688</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.8449989999999999</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44847879.936666</v>
+        <v>44848019.695407</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>18819742.564816</v>
+        <v>18819808.943763</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>-46.535199</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>18819696.019552</v>
+        <v>18819762.398499</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>44847883.971822</v>
+        <v>44848023.362178</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.8449989999999999</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44847883.11154</v>
+        <v>44848022.501897</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>18819743.972337</v>
+        <v>18819810.318957</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>-46.535199</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>18819697.427073</v>
+        <v>18819763.773694</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>44847886.840811</v>
+        <v>44848026.281448</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>-0.8449989999999999</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>44847885.98053</v>
+        <v>44848025.421167</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>18819745.274978</v>
+        <v>18819811.724922</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>-46.535199</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>18819698.729714</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>44847889.668907</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>-0.8449989999999999</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>44847888.808625</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>18819746.570316</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-46.535199</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>18819700.025052</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>44847892.839396</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>-0.8449989999999999</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>44847891.979114</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>18819748.068184</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>-46.535199</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>18819701.52292</v>
+        <v>18819765.179658</v>
       </c>
     </row>
   </sheetData>
@@ -9147,7 +8269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9346,276 +8468,166 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>48.687126</v>
+        <v>49.613911</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>326795.375</v>
+        <v>333543.0625</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>157754.09375</v>
+        <v>158564.921875</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>363509.5625</v>
+        <v>369736.875</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>47.728031</v>
+        <v>47.757408</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>320402.65625</v>
+        <v>320177.78125</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>155989.46875</v>
+        <v>154215.859375</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>356852</v>
+        <v>355909.59375</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>50.258366</v>
+        <v>48.801933</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>339555.21875</v>
+        <v>326021.34375</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>159863.984375</v>
+        <v>159713.90625</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>375855.71875</v>
+        <v>363488.6875</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>52.922115</v>
+        <v>41.330593</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>359556.21875</v>
+        <v>262683.53125</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>163275.640625</v>
+        <v>164698.921875</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>395805.34375</v>
+        <v>309099.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>48.687126</v>
+        <v>49.613911</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>326795.375</v>
+        <v>333543.0625</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>157754.09375</v>
+        <v>158564.921875</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>363509.5625</v>
+        <v>369736.875</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>48.052158</v>
+        <v>48.031013</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>322920</v>
+        <v>321860.3125</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>156350.71875</v>
+        <v>155328.890625</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>359289.25</v>
+        <v>357895.84375</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>50.129028</v>
+        <v>49.564331</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>339073.53125</v>
+        <v>330853.8125</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>158755.375</v>
+        <v>162477.09375</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>374936.40625</v>
+        <v>369022.5</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>50.483448</v>
+        <v>47.600746</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>341654.5625</v>
+        <v>312138.78125</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>160929.515625</v>
+        <v>168583.15625</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>378009.8125</v>
+        <v>354790.3125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>48.687126</v>
+        <v>49.613911</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>326795.375</v>
+        <v>333543.0625</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>157754.09375</v>
+        <v>158564.921875</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>363509.5625</v>
+        <v>369736.875</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>48.120754</v>
+        <v>48.348797</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>323606.375</v>
+        <v>323978.125</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>156164.203125</v>
+        <v>156320.5625</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>359825.59375</v>
+        <v>360224.125</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>48.127003</v>
+        <v>51.244053</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>324868.25</v>
+        <v>343795.5</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>154071.8125</v>
+        <v>164269.78125</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>360022.375</v>
+        <v>381493.65625</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>47.154087</v>
+        <v>57.711746</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>319877.53125</v>
+        <v>395822.125</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>148170.203125</v>
+        <v>164158.765625</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>352994.875</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>48.687126</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>326795.375</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>157754.09375</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>363509.5625</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>48.20134</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>324316.6875</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>156112.703125</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>360440.71875</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>48.935936</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>330423.03125</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>156222.828125</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>365966.625</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>50.142342</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>339622.65625</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>157576.015625</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>374762.625</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>48.687126</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>326795.375</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>157754.09375</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>363509.5625</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>48.389652</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>325650.53125</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>156598.5</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>361853.1875</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>49.540859</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>332582.53125</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>162080.078125</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>370445.0625</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>49.689335</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>327826.625</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>174553.671875</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>371502.15625</v>
+        <v>428672.59375</v>
       </c>
     </row>
   </sheetData>
@@ -9630,7 +8642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9856,7 +8868,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -9950,7 +8962,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -10044,7 +9056,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -10132,194 +9144,6 @@
         <v>0</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>1403</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>304</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1403</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>304</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10335,7 +9159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10617,7 +9441,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -10699,7 +9523,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -10781,7 +9605,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -10857,170 +9681,6 @@
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11036,7 +9696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11351,7 +10011,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 11:54:54</t>
+          <t>2026-05-13 12:19:57</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -11442,7 +10102,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:25</t>
+          <t>2026-05-13 12:20:27</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -11533,7 +10193,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 11:55:56</t>
+          <t>2026-05-13 12:20:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -11618,188 +10278,6 @@
         <v>0</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-13 11:56:59</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ab_meter_output/xlsx/ABMeter_10_16_130_50.xlsx
+++ b/ab_meter_output/xlsx/ABMeter_10_16_130_50.xlsx
@@ -208,12 +208,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$B$2:$B$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -240,12 +240,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$C$2:$C$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -272,12 +272,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$D$2:$D$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -304,12 +304,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$E$2:$E$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -336,12 +336,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$F$2:$F$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -368,12 +368,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$G$2:$G$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -400,12 +400,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$H$2:$H$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -432,12 +432,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$I$2:$I$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -464,12 +464,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$J$2:$J$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -496,12 +496,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$K$2:$K$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +528,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$L$2:$L$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +560,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Device_Configuration_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Device_Configuration_Table'!$M$2:$M$5</f>
+              <f>'Device_Configuration_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Device_Configuration_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -679,12 +679,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$B$2:$B$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -711,12 +711,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$C$2:$C$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -743,12 +743,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$D$2:$D$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -775,12 +775,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$E$2:$E$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -807,12 +807,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$F$2:$F$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -839,12 +839,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'MinMax_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'MinMax_Log_Table'!$G$2:$G$5</f>
+              <f>'MinMax_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MinMax_Log_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -958,12 +958,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$B$2:$B$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -990,12 +990,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$C$2:$C$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1022,12 +1022,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$D$2:$D$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1054,12 +1054,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$E$2:$E$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -1086,12 +1086,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$F$2:$F$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -1118,12 +1118,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$G$2:$G$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -1150,12 +1150,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$H$2:$H$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -1182,12 +1182,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$I$2:$I$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -1214,12 +1214,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$J$2:$J$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -1246,12 +1246,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$K$2:$K$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -1278,12 +1278,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$L$2:$L$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -1310,12 +1310,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table_Extended'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table_Extended'!$M$2:$M$5</f>
+              <f>'Diagnostic_Table_Extended'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table_Extended'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -1429,12 +1429,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$B$2:$B$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1461,12 +1461,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$C$2:$C$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1493,12 +1493,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$D$2:$D$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1525,12 +1525,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$E$2:$E$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -1557,12 +1557,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$F$2:$F$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -1589,12 +1589,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$G$2:$G$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -1621,12 +1621,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$H$2:$H$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -1653,12 +1653,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$I$2:$I$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -1685,12 +1685,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$J$2:$J$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -1717,12 +1717,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$K$2:$K$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -1749,12 +1749,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$L$2:$L$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -1781,12 +1781,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Communications_Configuration_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Communications_Configuration_Ta'!$M$2:$M$5</f>
+              <f>'Communications_Configuration_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Communications_Configuration_Ta'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -1900,12 +1900,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$B$2:$B$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1932,12 +1932,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$C$2:$C$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1964,12 +1964,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$D$2:$D$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1996,12 +1996,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$E$2:$E$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -2028,12 +2028,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$F$2:$F$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -2060,12 +2060,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$G$2:$G$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -2092,12 +2092,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$H$2:$H$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -2124,12 +2124,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$I$2:$I$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -2156,12 +2156,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$J$2:$J$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -2188,12 +2188,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$K$2:$K$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -2220,12 +2220,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$L$2:$L$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -2252,12 +2252,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Table'!$M$2:$M$5</f>
+              <f>'Voltage_Current_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -2371,12 +2371,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$B$2:$B$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -2403,12 +2403,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$C$2:$C$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -2435,12 +2435,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$D$2:$D$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -2467,12 +2467,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$E$2:$E$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -2499,12 +2499,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$F$2:$F$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -2531,12 +2531,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$G$2:$G$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -2563,12 +2563,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$H$2:$H$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -2595,12 +2595,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$I$2:$I$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -2627,12 +2627,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$J$2:$J$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -2659,12 +2659,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$K$2:$K$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -2691,12 +2691,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$L$2:$L$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -2723,12 +2723,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Real_Time_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Real_Time_Power_Table'!$M$2:$M$5</f>
+              <f>'Real_Time_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Real_Time_Power_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -2842,12 +2842,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$B$2:$B$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -2874,12 +2874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$C$2:$C$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -2906,12 +2906,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$D$2:$D$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -2938,12 +2938,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$E$2:$E$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -2970,12 +2970,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$F$2:$F$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -3002,12 +3002,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cumulative_Power_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cumulative_Power_Table'!$G$2:$G$5</f>
+              <f>'Cumulative_Power_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cumulative_Power_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -3121,12 +3121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$B$2:$B$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -3153,12 +3153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$C$2:$C$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -3185,12 +3185,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$D$2:$D$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -3217,12 +3217,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$E$2:$E$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -3249,12 +3249,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$F$2:$F$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -3281,12 +3281,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$G$2:$G$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -3313,12 +3313,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$H$2:$H$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -3345,12 +3345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$I$2:$I$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -3377,12 +3377,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$J$2:$J$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -3409,12 +3409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$K$2:$K$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -3441,12 +3441,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$L$2:$L$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -3473,12 +3473,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Demand_Data_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Demand_Data_Table'!$M$2:$M$5</f>
+              <f>'Demand_Data_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Demand_Data_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -3592,12 +3592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$B$2:$B$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -3624,12 +3624,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$C$2:$C$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -3656,12 +3656,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$D$2:$D$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -3688,12 +3688,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$E$2:$E$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -3720,12 +3720,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$F$2:$F$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -3752,12 +3752,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$G$2:$G$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -3784,12 +3784,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$H$2:$H$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -3816,12 +3816,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$I$2:$I$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -3848,12 +3848,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$J$2:$J$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -3880,12 +3880,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$K$2:$K$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -3912,12 +3912,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$L$2:$L$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -3944,12 +3944,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Diagnostic_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Diagnostic_Table'!$M$2:$M$5</f>
+              <f>'Diagnostic_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagnostic_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -4063,12 +4063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$B$2:$B$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -4095,12 +4095,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$C$2:$C$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -4127,12 +4127,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$D$2:$D$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -4159,12 +4159,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$E$2:$E$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -4191,12 +4191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$F$2:$F$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -4223,12 +4223,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$G$2:$G$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -4255,12 +4255,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$H$2:$H$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -4287,12 +4287,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$I$2:$I$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -4319,12 +4319,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$J$2:$J$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -4351,12 +4351,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$K$2:$K$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -4383,12 +4383,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$L$2:$L$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -4415,12 +4415,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Voltage_Current_Snapshot_Log_Ta'!$M$2:$M$5</f>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage_Current_Snapshot_Log_Ta'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -4534,12 +4534,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$B$2:$B$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -4566,12 +4566,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$C$2:$C$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -4598,12 +4598,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$D$2:$D$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -4630,12 +4630,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$E$2:$E$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -4662,12 +4662,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$F$2:$F$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -4694,12 +4694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$G$2:$G$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -4726,12 +4726,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$H$2:$H$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -4758,12 +4758,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$I$2:$I$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -4790,12 +4790,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$J$2:$J$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -4822,12 +4822,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$K$2:$K$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$K$2:$K$7</f>
             </numRef>
           </val>
         </ser>
@@ -4854,12 +4854,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$L$2:$L$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -4886,12 +4886,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Power_Snapshot_Log_Table'!$A$3:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Power_Snapshot_Log_Table'!$M$2:$M$5</f>
+              <f>'Power_Snapshot_Log_Table'!$A$3:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Power_Snapshot_Log_Table'!$M$2:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -4966,7 +4966,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -4993,7 +4993,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5020,7 +5020,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5047,7 +5047,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5074,7 +5074,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5101,7 +5101,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5128,7 +5128,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5155,7 +5155,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5182,7 +5182,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5209,7 +5209,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5236,7 +5236,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5040000"/>
@@ -5546,7 +5546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5836,7 +5836,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -5930,7 +5930,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6024,7 +6024,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6112,6 +6112,194 @@
         <v>2</v>
       </c>
       <c r="AD5" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2399.999756</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2399.999756</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6127,7 +6315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6192,7 +6380,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6217,7 +6405,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6242,7 +6430,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6261,6 +6449,56 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6276,7 +6514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6502,7 +6740,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6596,7 +6834,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6690,7 +6928,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6778,6 +7016,194 @@
         <v>0</v>
       </c>
       <c r="AD5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1403</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1403</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6793,7 +7219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6918,7 +7344,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6967,7 +7393,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -7016,7 +7442,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -7059,6 +7485,104 @@
         <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -7074,7 +7598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7335,71 +7859,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>48.402405</v>
+        <v>45.75425</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>52.484978</v>
+        <v>48.525005</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46.820866</v>
+        <v>42.113033</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.004291</v>
+        <v>0.003984</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>49.236084</v>
+        <v>45.464096</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>49.138004</v>
+        <v>45.349667</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>3.420535</v>
+        <v>3.763814</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>6.961078</v>
+        <v>8.299541</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4313.118164</v>
+        <v>4332.235352</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>4283.645508</v>
+        <v>4301.313477</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>4302.740723</v>
+        <v>4314.799316</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>4299.834473</v>
+        <v>4316.115723</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>4298.916504</v>
+        <v>4315.239746</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>29.667421</v>
+        <v>31.454617</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.690114</v>
+        <v>0.728919</v>
       </c>
       <c r="R3" s="3" t="n">
+        <v>2500.284424</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>2491.706055</v>
       </c>
-      <c r="S3" s="3" t="n">
-        <v>2479.79126</v>
-      </c>
       <c r="T3" s="3" t="n">
-        <v>2475.144775</v>
+        <v>2482.77002</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>2482.213867</v>
+        <v>2491.58667</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>59.974606</v>
+        <v>60.012691</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>2</v>
@@ -7408,71 +7932,71 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>48.843761</v>
+        <v>47.090588</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>53.527077</v>
+        <v>50.020721</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>48.390144</v>
+        <v>43.988811</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.003984</v>
+        <v>0.004291</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>50.253662</v>
+        <v>47.033375</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>50.167839</v>
+        <v>46.931206</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3.297935</v>
+        <v>3.543134</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>6.573802</v>
+        <v>7.549634</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4311.813477</v>
+        <v>4323.440918</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>4282.809082</v>
+        <v>4294.751953</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>4299.278809</v>
+        <v>4308.596191</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>4297.967285</v>
+        <v>4308.929688</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>4297.129395</v>
+        <v>4308.09082</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>29.905714</v>
+        <v>30.144007</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.695946</v>
+        <v>0.699707</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>2490.037842</v>
+        <v>2495.876221</v>
       </c>
       <c r="S4" s="3" t="n">
+        <v>2486.940186</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>2479.672119</v>
       </c>
-      <c r="T4" s="3" t="n">
-        <v>2473.714844</v>
-      </c>
       <c r="U4" s="3" t="n">
-        <v>2481.141602</v>
+        <v>2487.496094</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>59.962887</v>
+        <v>60.032223</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>2</v>
@@ -7481,73 +8005,219 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>52.00684</v>
+        <v>46.906685</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>56.371391</v>
+        <v>49.640663</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>49.98394</v>
+        <v>43.596493</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0.003984</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>52.787395</v>
+        <v>46.714615</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>52.681137</v>
+        <v>46.612446</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3.788334</v>
+        <v>3.555394</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>7.191063</v>
+        <v>7.627564</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4311.807617</v>
+        <v>4326.293945</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>4281.977539</v>
+        <v>4295.585938</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>4296.656738</v>
+        <v>4311.697754</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>4296.813965</v>
+        <v>4311.192871</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>4295.937988</v>
+        <v>4310.235352</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>30.501446</v>
+        <v>30.978031</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7100070000000001</v>
+        <v>0.718709</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>2489.203857</v>
+        <v>2497.901611</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>2479.79126</v>
+        <v>2487.77417</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>2472.404297</v>
+        <v>2480.625488</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2480.466553</v>
+        <v>2488.76709</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>59.992184</v>
+        <v>60.020504</v>
       </c>
       <c r="W5" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>46.747307</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>49.652924</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>43.289993</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.003984</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>46.563404</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>46.453068</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>3.714774</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>7.996833</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4325.820312</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4295.34668</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>4310.026367</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>4310.397949</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>4309.520508</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>30.978031</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.718828</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>2497.186768</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>2487.893311</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>2479.9104</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>2488.330078</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>60.015621</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>47.090588</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>50.351742</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>44.099152</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.003984</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>47.180492</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>47.078327</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>3.653474</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>7.760417</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>4325.105469</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>4296.063477</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>4310.027344</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>4310.398926</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>4309.520508</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>30.382299</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.705004</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>2496.829346</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>2487.893311</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>2480.268066</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>2488.330322</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>60.023434</v>
+      </c>
+      <c r="W7" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7563,7 +8233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7850,238 +8520,396 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>104529.257812</v>
+        <v>100723.695312</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>117357.421875</v>
+        <v>112260.054688</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>106315.414062</v>
+        <v>97267.953125</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>328202.09375</v>
+        <v>310251.6875</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>60094.707031</v>
+        <v>54318.441406</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>56197.335938</v>
+        <v>45088.957031</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>45899.300781</v>
+        <v>38422.039062</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>162191.34375</v>
+        <v>137829.4375</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>120562.429688</v>
+        <v>114454.46875</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>130109.671875</v>
+        <v>120971.0625</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>115827.695312</v>
+        <v>104592.359375</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>366499.78125</v>
+        <v>340017.875</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-86.70135500000001</v>
+        <v>-88.003288</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-90.19884500000001</v>
+        <v>-92.799103</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-91.78756</v>
+        <v>-92.997185</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-89.557129</v>
+        <v>-91.23764799999999</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>-86.36116</v>
+        <v>-87.54334299999999</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-90.385689</v>
+        <v>-90.991135</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-91.902817</v>
+        <v>-91.470337</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>-89.66894499999999</v>
+        <v>-90.070595</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>99.989403</v>
+        <v>99.99095199999999</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>99.987785</v>
+        <v>99.987892</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>99.97803500000001</v>
+        <v>99.983253</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>99.985077</v>
+        <v>99.98736599999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>105864.4375</v>
+        <v>102046.8125</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>118820.492188</v>
+        <v>113843.90625</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110023.851562</v>
+        <v>100003.1875</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>334708.78125</v>
+        <v>315893.90625</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>59793.960938</v>
+        <v>56451.808594</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>58868.816406</v>
+        <v>48727.648438</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>46910.921875</v>
+        <v>41073.046875</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>165573.703125</v>
+        <v>146252.5</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>121598.078125</v>
+        <v>116633.742188</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>132595.203125</v>
+        <v>123831.007812</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>119606.617188</v>
+        <v>108135.320312</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>373799.90625</v>
+        <v>348600.0625</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-87.06094400000001</v>
+        <v>-87.493385</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-89.611458</v>
+        <v>-91.934898</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-91.98809799999999</v>
+        <v>-92.479668</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-89.54257200000001</v>
+        <v>-90.548294</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-86.36116</v>
+        <v>-88.38562</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-90.385689</v>
+        <v>-92.37384</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-91.902817</v>
+        <v>-92.66102600000001</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>-89.66894499999999</v>
+        <v>10.164859</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>99.989403</v>
+        <v>99.990082</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>99.987785</v>
+        <v>99.986076</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>99.97803500000001</v>
+        <v>99.977379</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>99.985077</v>
+        <v>99.98452</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>112917.921875</v>
+        <v>102057.28125</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>126870.546875</v>
+        <v>113322.90625</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>113982.828125</v>
+        <v>99429.085938</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>353771.3125</v>
+        <v>314809.28125</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>62870.144531</v>
+        <v>56934.949219</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>58188.886719</v>
+        <v>48661.273438</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>47224.851562</v>
+        <v>41641.539062</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>168283.875</v>
+        <v>147237.75</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>129241.929688</v>
+        <v>116867.546875</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>139552.78125</v>
+        <v>123317.578125</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>123380.210938</v>
+        <v>107822.328125</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>392174.9375</v>
+        <v>348007.4375</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-87.369415</v>
+        <v>-87.32730100000001</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-90.91223100000001</v>
+        <v>-91.895172</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-92.383392</v>
+        <v>-92.215675</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-90.20291899999999</v>
+        <v>-90.460381</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-86.977852</v>
+        <v>-88.38562</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-90.564804</v>
+        <v>-92.37384</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-92.00505800000001</v>
+        <v>-92.66102600000001</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-89.949951</v>
+        <v>10.164859</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>99.98922</v>
+        <v>99.990082</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>99.98777800000001</v>
+        <v>99.986076</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>99.977936</v>
+        <v>99.977379</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>99.984978</v>
+        <v>99.98452</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>102074.765625</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>113804.085938</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>99205.28125</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>315084.125</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>56921.300781</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>48351.550781</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>41114.554688</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>146387.40625</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>116884.1875</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>123647.210938</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>107410.898438</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>347942.3125</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-87.32983400000001</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-92.039345</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-92.360535</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-90.55729700000001</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>-88.38562</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-92.37384</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-92.66102600000001</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>10.164859</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>99.990082</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>99.986076</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>99.977379</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>99.98452</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>102789.09375</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>115011.460938</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>101187.945312</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>318988.5</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>56897.925781</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>49543.414062</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>41308.632812</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>147749.96875</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>117493.445312</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>125227.234375</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>109306.335938</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>352027.03125</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-87.484962</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-91.84221599999999</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>-92.572807</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-90.620789</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>-88.38562</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-92.37384</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-92.66102600000001</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>10.164859</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>99.990082</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>99.986076</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>99.977379</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>99.98452</v>
       </c>
     </row>
   </sheetData>
@@ -8096,7 +8924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8185,76 +9013,126 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>44848020.555688</v>
+        <v>44848103.112886</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.8449989999999999</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44848019.695407</v>
+        <v>44848102.252604</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>18819808.943763</v>
+        <v>18819847.402874</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>-46.535199</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>18819762.398499</v>
+        <v>18819800.85761</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>44848023.362178</v>
+        <v>44848104.420193</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.8449989999999999</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44848022.501897</v>
+        <v>44848103.559911</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>18819810.318957</v>
+        <v>18819847.985341</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>-46.535199</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>18819763.773694</v>
+        <v>18819801.440077</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>44848026.281448</v>
+        <v>44848105.764634</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>-0.8449989999999999</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>44848025.421167</v>
+        <v>44848104.904353</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>18819811.724922</v>
+        <v>18819848.605531</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>-46.535199</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>18819765.179658</v>
+        <v>18819802.060267</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>44848107.10277</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-0.8449989999999999</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>44848106.242489</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>18819849.231388</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-46.535199</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>18819802.686124</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>44848108.446881</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-0.8449989999999999</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>44848107.5866</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>18819849.85373</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-46.535199</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>18819803.308466</v>
       </c>
     </row>
   </sheetData>
@@ -8269,7 +9147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8468,166 +9346,276 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>49.613911</v>
+        <v>47.903145</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>333543.0625</v>
+        <v>322211.3125</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>158564.921875</v>
+        <v>151798.640625</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>369736.875</v>
+        <v>356603.25</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>47.757408</v>
+        <v>47.604218</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>320177.78125</v>
+        <v>320961.5</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>154215.859375</v>
+        <v>148445.203125</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>355909.59375</v>
+        <v>354068.125</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>48.801933</v>
+        <v>46.082771</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>326021.34375</v>
+        <v>313205.125</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>159713.90625</v>
+        <v>140821.90625</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>363488.6875</v>
+        <v>343929.34375</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>41.330593</v>
+        <v>36.857258</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>262683.53125</v>
+        <v>244951.34375</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>164698.921875</v>
+        <v>126279.742188</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>309099.25</v>
+        <v>275713.65625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>49.613911</v>
+        <v>47.903145</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>333543.0625</v>
+        <v>322211.3125</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>158564.921875</v>
+        <v>151798.640625</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>369736.875</v>
+        <v>356603.25</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>48.031013</v>
+        <v>47.49897</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>321860.3125</v>
+        <v>320435.875</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>155328.890625</v>
+        <v>147909.75</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>357895.84375</v>
+        <v>353371.09375</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>49.564331</v>
+        <v>46.685856</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>330853.8125</v>
+        <v>315976.34375</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>162477.09375</v>
+        <v>145128.171875</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>369022.5</v>
+        <v>348209.59375</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>47.600746</v>
+        <v>51.995132</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>312138.78125</v>
+        <v>339799.25</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>168583.15625</v>
+        <v>184358.75</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>354790.3125</v>
+        <v>385893.15625</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>49.613911</v>
+        <v>47.903145</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>333543.0625</v>
+        <v>322211.3125</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>158564.921875</v>
+        <v>151798.640625</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>369736.875</v>
+        <v>356603.25</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>48.348797</v>
+        <v>47.456139</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>323978.125</v>
+        <v>320209.96875</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>156320.5625</v>
+        <v>147801.390625</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>360224.125</v>
+        <v>353120.84375</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>51.244053</v>
+        <v>46.928501</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>343795.5</v>
+        <v>316887.6875</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>164269.78125</v>
+        <v>147523.03125</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>381493.65625</v>
+        <v>350011.9375</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>57.711746</v>
+        <v>54.053143</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>395822.125</v>
+        <v>348389.8125</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>164158.765625</v>
+        <v>203317.546875</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>428672.59375</v>
+        <v>401831.34375</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>47.903145</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>322211.3125</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>151798.640625</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>356603.25</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>47.41325</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>319931.84375</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>147764.53125</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>352855.46875</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>46.832363</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>316375.09375</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>146698.828125</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>349222.9375</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>47.284698</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>315255.6875</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>154439.6875</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>351818.375</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>47.903145</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>322211.3125</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>151798.640625</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>356603.25</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>47.393669</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>319837.6875</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>147739.421875</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>352761.625</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>47.231365</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>319207.40625</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>147857.9375</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>352265.78125</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>50.827873</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>344506.15625</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>158445</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>379606.84375</v>
       </c>
     </row>
   </sheetData>
@@ -8642,7 +9630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8868,7 +9856,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -8962,7 +9950,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -9056,7 +10044,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -9144,6 +10132,194 @@
         <v>0</v>
       </c>
       <c r="AD5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1403</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1403</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9159,7 +10335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9441,7 +10617,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -9523,7 +10699,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -9605,7 +10781,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -9681,6 +10857,170 @@
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9696,7 +11036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10011,7 +11351,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:19:57</t>
+          <t>2026-05-13 12:35:18</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -10102,7 +11442,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:27</t>
+          <t>2026-05-13 12:35:33</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -10193,7 +11533,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:20:58</t>
+          <t>2026-05-13 12:35:49</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -10278,6 +11618,188 @@
         <v>0</v>
       </c>
       <c r="AC5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:36:19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ab_meter_output/xlsx/ABMeter_10_16_130_50.xlsx
+++ b/ab_meter_output/xlsx/ABMeter_10_16_130_50.xlsx
@@ -5836,7 +5836,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -5930,7 +5930,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6024,7 +6024,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6118,7 +6118,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -6212,7 +6212,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -6380,7 +6380,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6405,7 +6405,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6430,7 +6430,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -6455,7 +6455,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -6480,7 +6480,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -6740,7 +6740,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -6834,7 +6834,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -6928,7 +6928,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -7022,7 +7022,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -7116,7 +7116,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -7344,7 +7344,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -7393,7 +7393,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -7442,7 +7442,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -7491,7 +7491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -7540,7 +7540,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -7859,71 +7859,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>45.75425</v>
+        <v>46.146568</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>48.525005</v>
+        <v>51.47966</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>42.113033</v>
+        <v>43.792652</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.003984</v>
+        <v>0.004291</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>45.464096</v>
+        <v>47.139629</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>45.349667</v>
+        <v>46.980247</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>3.763814</v>
+        <v>4.695572</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>8.299541</v>
+        <v>9.994781</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4332.235352</v>
+        <v>4305.156738</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>4301.313477</v>
+        <v>4276.12793</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>4314.799316</v>
+        <v>4292.597656</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>4316.115723</v>
+        <v>4291.294434</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>4315.239746</v>
+        <v>4290.457031</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>31.454617</v>
+        <v>29.548275</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.728919</v>
+        <v>0.688698</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>2500.284424</v>
+        <v>2486.225342</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2491.706055</v>
+        <v>2475.859619</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>2482.77002</v>
+        <v>2469.783203</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>2491.58667</v>
+        <v>2477.289307</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>60.012691</v>
+        <v>59.983395</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>2</v>
@@ -7932,71 +7932,71 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>47.090588</v>
+        <v>45.263847</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>50.020721</v>
+        <v>49.836823</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>43.988811</v>
+        <v>42.444054</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0.004291</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>47.033375</v>
+        <v>45.84824</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>46.931206</v>
+        <v>45.705208</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3.543134</v>
+        <v>4.425853</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>7.549634</v>
+        <v>9.683476000000001</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4323.440918</v>
+        <v>4316.439453</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>4294.751953</v>
+        <v>4288.541504</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>4308.596191</v>
+        <v>4304.533691</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>4308.929688</v>
+        <v>4303.171387</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>4308.09082</v>
+        <v>4302.25293</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>30.144007</v>
+        <v>29.309982</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.699707</v>
+        <v>0.681271</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>2495.876221</v>
+        <v>2492.77832</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2486.940186</v>
+        <v>2482.650879</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2479.672119</v>
+        <v>2477.051025</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>2487.496094</v>
+        <v>2484.160156</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>60.032223</v>
+        <v>59.995113</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>2</v>
@@ -8005,68 +8005,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46.906685</v>
+        <v>44.344349</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>49.640663</v>
+        <v>49.358681</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>43.596493</v>
+        <v>42.395012</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.003984</v>
+        <v>0.004291</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46.714615</v>
+        <v>45.366016</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>46.612446</v>
+        <v>45.22707</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3.555394</v>
+        <v>4.241953</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>7.627564</v>
+        <v>9.379235</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4326.293945</v>
+        <v>4316.434082</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>4295.585938</v>
+        <v>4288.90332</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>4311.697754</v>
+        <v>4304.537109</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>4311.192871</v>
+        <v>4303.291504</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>4310.235352</v>
+        <v>4302.491211</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>30.978031</v>
+        <v>29.190836</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.718709</v>
+        <v>0.678464</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>2497.901611</v>
+        <v>2492.65918</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>2487.77417</v>
+        <v>2482.77002</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>2480.625488</v>
+        <v>2477.170166</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2488.76709</v>
+        <v>2484.199951</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>60.020504</v>
@@ -8078,68 +8078,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46.747307</v>
+        <v>44.712151</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>49.652924</v>
+        <v>50.032982</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>43.289993</v>
+        <v>42.345974</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0.003984</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46.563404</v>
+        <v>45.697037</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>46.453068</v>
+        <v>45.533569</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>3.714774</v>
+        <v>4.658792</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>7.996833</v>
+        <v>10.231556</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4325.820312</v>
+        <v>4313.228027</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4295.34668</v>
+        <v>4287.350586</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4310.026367</v>
+        <v>4302.984863</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>4310.397949</v>
+        <v>4301.1875</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>4309.520508</v>
+        <v>4300.346191</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>30.978031</v>
+        <v>28.118521</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.718828</v>
+        <v>0.6538659999999999</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>2497.186768</v>
+        <v>2491.229492</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>2487.893311</v>
+        <v>2481.221191</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>2479.9104</v>
+        <v>2476.574463</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>2488.330078</v>
+        <v>2483.008545</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>60.015621</v>
@@ -8151,71 +8151,71 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>47.090588</v>
+        <v>44.47921</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>50.351742</v>
+        <v>49.922642</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>44.099152</v>
+        <v>42.713772</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.003984</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>47.180492</v>
+        <v>45.705212</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>47.078327</v>
+        <v>45.558086</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>3.653474</v>
+        <v>4.450373</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>7.760417</v>
+        <v>9.768568</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4325.105469</v>
+        <v>4310.734375</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>4296.063477</v>
+        <v>4285.320801</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>4310.027344</v>
+        <v>4299.881348</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>4310.398926</v>
+        <v>4298.64502</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>4309.520508</v>
+        <v>4297.844238</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>30.382299</v>
+        <v>27.880228</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.705004</v>
+        <v>0.648703</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>2496.829346</v>
+        <v>2489.442139</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>2487.893311</v>
+        <v>2480.029541</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>2480.268066</v>
+        <v>2475.144775</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2488.330322</v>
+        <v>2481.538818</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>60.023434</v>
+        <v>60.012691</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>2</v>
@@ -8520,396 +8520,396 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>100723.695312</v>
+        <v>100393.5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>112260.054688</v>
+        <v>117520.085938</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>97267.953125</v>
+        <v>101743.257812</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>310251.6875</v>
+        <v>319656.84375</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>54318.441406</v>
+        <v>55366.519531</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>45088.957031</v>
+        <v>48191.128906</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>38422.039062</v>
+        <v>35319.027344</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>137829.4375</v>
+        <v>138876.671875</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>114454.46875</v>
+        <v>114655.75</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>120971.0625</v>
+        <v>127007.125</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>104592.359375</v>
+        <v>107709.304688</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>340017.875</v>
+        <v>349372.1875</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-88.003288</v>
+        <v>-87.560806</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-92.799103</v>
+        <v>-92.530304</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-92.997185</v>
+        <v>-94.46096799999999</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-91.23764799999999</v>
+        <v>-91.48867799999999</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>-87.54334299999999</v>
+        <v>-88.022018</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-90.991135</v>
+        <v>-92.08427399999999</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-91.470337</v>
+        <v>-94.03254699999999</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>-90.070595</v>
+        <v>-91.54866800000001</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>99.99095199999999</v>
+        <v>99.98737300000001</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>99.987892</v>
+        <v>99.987076</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>99.983253</v>
+        <v>99.975403</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>99.98736599999999</v>
+        <v>99.983284</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>102046.8125</v>
+        <v>97524.109375</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>113843.90625</v>
+        <v>113775.851562</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>100003.1875</v>
+        <v>98204.96875</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>315893.90625</v>
+        <v>309504.9375</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>56451.808594</v>
+        <v>55945.859375</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>48727.648438</v>
+        <v>48359.6875</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>41073.046875</v>
+        <v>36703.660156</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>146252.5</v>
+        <v>141009.203125</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>116633.742188</v>
+        <v>112430.015625</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>123831.007812</v>
+        <v>123630.101562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>108135.320312</v>
+        <v>104857.679688</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>348600.0625</v>
+        <v>340917.8125</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-87.493385</v>
+        <v>-86.742058</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-91.934898</v>
+        <v>-92.02924299999999</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-92.479668</v>
+        <v>-93.65548699999999</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-90.548294</v>
+        <v>-90.791962</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-88.38562</v>
+        <v>-88.022018</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-92.37384</v>
+        <v>-92.08427399999999</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-92.66102600000001</v>
+        <v>-94.03254699999999</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>10.164859</v>
+        <v>-91.54866800000001</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>99.990082</v>
+        <v>99.98737300000001</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>99.986076</v>
+        <v>99.987076</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>99.977379</v>
+        <v>99.975403</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>99.98452</v>
+        <v>99.983284</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>102057.28125</v>
+        <v>96460.320312</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>113322.90625</v>
+        <v>112640.078125</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>99429.085938</v>
+        <v>98455.796875</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>314809.28125</v>
+        <v>307556.1875</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>56934.949219</v>
+        <v>54035.082031</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>48661.273438</v>
+        <v>48234.226562</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>41641.539062</v>
+        <v>36028.683594</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>147237.75</v>
+        <v>138298</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>116867.546875</v>
+        <v>110549.992188</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>123317.578125</v>
+        <v>122540.328125</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>107822.328125</v>
+        <v>104852.625</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>348007.4375</v>
+        <v>337942.9375</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-87.32730100000001</v>
+        <v>-87.254936</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-91.895172</v>
+        <v>-91.920822</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-92.215675</v>
+        <v>-93.899216</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-90.460381</v>
+        <v>-91.015411</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-88.38562</v>
+        <v>-87.637421</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-92.37384</v>
+        <v>-92.49128</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-92.66102600000001</v>
+        <v>-94.319168</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>10.164859</v>
+        <v>-91.696236</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>99.990082</v>
+        <v>99.987656</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>99.986076</v>
+        <v>99.985657</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>99.977379</v>
+        <v>99.973885</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>99.98452</v>
+        <v>99.982399</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>102074.765625</v>
+        <v>96355.710938</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>113804.085938</v>
+        <v>113921.21875</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>99205.28125</v>
+        <v>98337.71875</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>315084.125</v>
+        <v>308614.65625</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>56921.300781</v>
+        <v>56011.671875</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>48351.550781</v>
+        <v>49178.816406</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>41114.554688</v>
+        <v>36241.742188</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>146387.40625</v>
+        <v>141432.21875</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>116884.1875</v>
+        <v>111465.226562</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>123647.210938</v>
+        <v>124100.53125</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>107410.898438</v>
+        <v>104817.195312</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>347942.3125</v>
+        <v>340382.9375</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-87.32983400000001</v>
+        <v>-86.444633</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-92.039345</v>
+        <v>-91.797523</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-92.360535</v>
+        <v>-93.81830600000001</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-90.55729700000001</v>
+        <v>-90.63299600000001</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-88.38562</v>
+        <v>-87.637421</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-92.37384</v>
+        <v>-92.49128</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-92.66102600000001</v>
+        <v>-94.319168</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>10.164859</v>
+        <v>-91.696236</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>99.990082</v>
+        <v>99.987656</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>99.986076</v>
+        <v>99.985657</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>99.977379</v>
+        <v>99.973885</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>99.98452</v>
+        <v>99.982399</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>102789.09375</v>
+        <v>96550.164062</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>115011.460938</v>
+        <v>113709.9375</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>101187.945312</v>
+        <v>99452.273438</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>318988.5</v>
+        <v>309712.375</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>56897.925781</v>
+        <v>54181.667969</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>49543.414062</v>
+        <v>48822.632812</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>41308.632812</v>
+        <v>35519.742188</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>147749.96875</v>
+        <v>138524.03125</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>117493.445312</v>
+        <v>110733.695312</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>125227.234375</v>
+        <v>123754.71875</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>109306.335938</v>
+        <v>105606.414062</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>352027.03125</v>
+        <v>340094.8125</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-87.484962</v>
+        <v>-87.191315</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-91.84221599999999</v>
+        <v>-91.883308</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>-92.572807</v>
+        <v>-94.172569</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>-90.620789</v>
+        <v>-91.07254</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-88.38562</v>
+        <v>-87.182625</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-92.37384</v>
+        <v>-91.928642</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-92.66102600000001</v>
+        <v>-93.91456599999999</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>10.164859</v>
+        <v>10.106877</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>99.990082</v>
+        <v>99.986465</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>99.986076</v>
+        <v>99.98442799999999</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>99.977379</v>
+        <v>99.972549</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>99.98452</v>
+        <v>99.98114</v>
       </c>
     </row>
   </sheetData>
@@ -9013,126 +9013,126 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>44848103.112886</v>
+        <v>44848144.059656</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.8449989999999999</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44848102.252604</v>
+        <v>44848143.199374</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>18819847.402874</v>
+        <v>18819866.164113</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>-46.535199</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>18819800.85761</v>
+        <v>18819819.618849</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>44848104.420193</v>
+        <v>44848146.746236</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.8449989999999999</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44848103.559911</v>
+        <v>44848145.885955</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>18819847.985341</v>
+        <v>18819867.362836</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>-46.535199</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>18819801.440077</v>
+        <v>18819820.817572</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>44848105.764634</v>
+        <v>44848149.343592</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>-0.8449989999999999</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>44848104.904353</v>
+        <v>44848148.483311</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>18819848.605531</v>
+        <v>18819868.541315</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>-46.535199</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>18819802.060267</v>
+        <v>18819821.996051</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>44848107.10277</v>
+        <v>44848151.961755</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>-0.8449989999999999</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>44848106.242489</v>
+        <v>44848151.101474</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>18819849.231388</v>
+        <v>18819869.727125</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>-46.535199</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>18819802.686124</v>
+        <v>18819823.181861</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>44848108.446881</v>
+        <v>44848154.566051</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.8449989999999999</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>44848107.5866</v>
+        <v>44848153.70577</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>18819849.85373</v>
+        <v>18819870.899913</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>-46.535199</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>18819803.308466</v>
+        <v>18819824.35465</v>
       </c>
     </row>
   </sheetData>
@@ -9346,7 +9346,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -9362,46 +9362,46 @@
         <v>356603.25</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>47.604218</v>
+        <v>47.369148</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>320961.5</v>
+        <v>320165.5</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>148445.203125</v>
+        <v>147206.71875</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>354068.125</v>
+        <v>352925.21875</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>46.082771</v>
+        <v>47.304859</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>313205.125</v>
+        <v>320123.5</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>140821.90625</v>
+        <v>145548.40625</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>343929.34375</v>
+        <v>352272.15625</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>36.857258</v>
+        <v>47.552708</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>244951.34375</v>
+        <v>321665.625</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>126279.742188</v>
+        <v>146353.25</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>275713.65625</v>
+        <v>354037.46875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -9417,46 +9417,46 @@
         <v>356603.25</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>47.49897</v>
+        <v>47.337666</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>320435.875</v>
+        <v>320007.1875</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>147909.75</v>
+        <v>146953.59375</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>353371.09375</v>
+        <v>352688.5625</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>46.685856</v>
+        <v>47.095123</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>315976.34375</v>
+        <v>318420</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>145128.171875</v>
+        <v>146009.1875</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>348209.59375</v>
+        <v>350892.3125</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>51.995132</v>
+        <v>46.851521</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>339799.25</v>
+        <v>316500.75</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>184358.75</v>
+        <v>145867.171875</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>385893.15625</v>
+        <v>349090.28125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -9472,46 +9472,46 @@
         <v>356603.25</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>47.456139</v>
+        <v>47.260914</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>320209.96875</v>
+        <v>319509.78125</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>147801.390625</v>
+        <v>146662.796875</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>353120.84375</v>
+        <v>352122.6875</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>46.928501</v>
+        <v>47.022945</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>316887.6875</v>
+        <v>318022.03125</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>147523.03125</v>
+        <v>145621.015625</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>350011.9375</v>
+        <v>350360.1875</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>54.053143</v>
+        <v>47.071236</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>348389.8125</v>
+        <v>318507.40625</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>203317.546875</v>
+        <v>145355.234375</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>401831.34375</v>
+        <v>350692.21875</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -9527,46 +9527,46 @@
         <v>356603.25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>47.41325</v>
+        <v>47.197212</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>319931.84375</v>
+        <v>319101.03125</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>147764.53125</v>
+        <v>146402.171875</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>352855.46875</v>
+        <v>351649.90625</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>46.832363</v>
+        <v>47.044186</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>316375.09375</v>
+        <v>318070.125</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>146698.828125</v>
+        <v>145840.390625</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>349222.9375</v>
+        <v>350502.46875</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>47.284698</v>
+        <v>47.028316</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>315255.6875</v>
+        <v>317868.65625</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>154439.6875</v>
+        <v>145923.453125</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>351818.375</v>
+        <v>350364.46875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -9582,40 +9582,40 @@
         <v>356603.25</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>47.393669</v>
+        <v>47.13216</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>319837.6875</v>
+        <v>318683.90625</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>147739.421875</v>
+        <v>146117.453125</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>352761.625</v>
+        <v>351161.25</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>47.231365</v>
+        <v>47.053001</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>319207.40625</v>
+        <v>318196</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>147857.9375</v>
+        <v>145697.625</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>352265.78125</v>
+        <v>350557.65625</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>50.827873</v>
+        <v>47.064873</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>344506.15625</v>
+        <v>318276.375</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>158445</v>
+        <v>145713.90625</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>379606.84375</v>
+        <v>350637.65625</v>
       </c>
     </row>
   </sheetData>
@@ -9856,7 +9856,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -9950,7 +9950,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -10044,7 +10044,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -10138,7 +10138,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -10232,7 +10232,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -10617,7 +10617,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -10699,7 +10699,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -10781,7 +10781,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -10863,7 +10863,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -10945,7 +10945,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -11351,7 +11351,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:18</t>
+          <t>2026-05-13 12:42:59</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -11442,7 +11442,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:33</t>
+          <t>2026-05-13 12:43:30</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -11533,7 +11533,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13 12:35:49</t>
+          <t>2026-05-13 12:44:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -11624,7 +11624,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:04</t>
+          <t>2026-05-13 12:44:31</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -11715,7 +11715,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13 12:36:19</t>
+          <t>2026-05-13 12:45:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
